--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126089652</v>
+        <v>126091848</v>
       </c>
       <c r="B2" t="n">
-        <v>103396</v>
+        <v>100428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609923</v>
+        <v>610126</v>
       </c>
       <c r="R2" t="n">
-        <v>7020292</v>
+        <v>7020167</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126089443</v>
+        <v>126090563</v>
       </c>
       <c r="B3" t="n">
         <v>100428</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609913</v>
+        <v>609902</v>
       </c>
       <c r="R3" t="n">
-        <v>7020279</v>
+        <v>7020332</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126089826</v>
+        <v>126092313</v>
       </c>
       <c r="B4" t="n">
         <v>100428</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>609916</v>
+        <v>610186</v>
       </c>
       <c r="R4" t="n">
-        <v>7020317</v>
+        <v>7020158</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -963,6 +963,2431 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126092513</v>
+      </c>
+      <c r="B5" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>610128</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7020092</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126091604</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>610001</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7020250</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126091741</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>610079</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7020222</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126092279</v>
+      </c>
+      <c r="B8" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>610202</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7020149</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126089652</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103396</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>609923</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7020292</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126090793</v>
+      </c>
+      <c r="B10" t="n">
+        <v>103396</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>609929</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7020293</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126091900</v>
+      </c>
+      <c r="B11" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>610133</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7020150</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126091974</v>
+      </c>
+      <c r="B12" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>610174</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7020149</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126091481</v>
+      </c>
+      <c r="B13" t="n">
+        <v>105182</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>609967</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7020285</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126092468</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>610149</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7020112</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126089443</v>
+      </c>
+      <c r="B15" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>609913</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7020279</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126090197</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97217</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>609878</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7020293</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126091251</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>609946</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7020274</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126091802</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105182</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221101</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Springkorn</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Impatiens noli-tangere</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>610110</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7020178</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126089826</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>609916</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7020317</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126090758</v>
+      </c>
+      <c r="B20" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>609938</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7020289</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126091989</v>
+      </c>
+      <c r="B21" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>610165</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7020164</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126091759</v>
+      </c>
+      <c r="B22" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>610090</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7020200</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126091224</v>
+      </c>
+      <c r="B23" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>609958</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7020289</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126090677</v>
+      </c>
+      <c r="B24" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>609919</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7020325</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126090868</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>609934</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7020301</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126091958</v>
+      </c>
+      <c r="B26" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>610148</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7020132</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126091696</v>
+      </c>
+      <c r="B27" t="n">
+        <v>103396</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>610047</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7020226</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126092414</v>
+      </c>
+      <c r="B28" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>610159</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7020117</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126090465</v>
+      </c>
+      <c r="B29" t="n">
+        <v>100428</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>609876</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7020328</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091251</v>
+        <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>100428</v>
+        <v>105182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609946</v>
+        <v>610110</v>
       </c>
       <c r="R17" t="n">
-        <v>7020274</v>
+        <v>7020178</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091802</v>
+        <v>126091251</v>
       </c>
       <c r="B18" t="n">
-        <v>105182</v>
+        <v>100428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,16 +2238,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>610110</v>
+        <v>609946</v>
       </c>
       <c r="R18" t="n">
-        <v>7020178</v>
+        <v>7020274</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091224</v>
+        <v>126090677</v>
       </c>
       <c r="B23" t="n">
         <v>100428</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609958</v>
+        <v>609919</v>
       </c>
       <c r="R23" t="n">
-        <v>7020289</v>
+        <v>7020325</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126090677</v>
+        <v>126091224</v>
       </c>
       <c r="B24" t="n">
         <v>100428</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609919</v>
+        <v>609958</v>
       </c>
       <c r="R24" t="n">
-        <v>7020325</v>
+        <v>7020289</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126092414</v>
+        <v>126090465</v>
       </c>
       <c r="B28" t="n">
         <v>100428</v>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>610159</v>
+        <v>609876</v>
       </c>
       <c r="R28" t="n">
-        <v>7020117</v>
+        <v>7020328</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126090465</v>
+        <v>126092414</v>
       </c>
       <c r="B29" t="n">
         <v>100428</v>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609876</v>
+        <v>610159</v>
       </c>
       <c r="R29" t="n">
-        <v>7020328</v>
+        <v>7020117</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126092279</v>
+        <v>126089652</v>
       </c>
       <c r="B8" t="n">
-        <v>100428</v>
+        <v>103396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610202</v>
+        <v>609923</v>
       </c>
       <c r="R8" t="n">
-        <v>7020149</v>
+        <v>7020292</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126089652</v>
+        <v>126092279</v>
       </c>
       <c r="B9" t="n">
-        <v>103396</v>
+        <v>100428</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609923</v>
+        <v>610202</v>
       </c>
       <c r="R9" t="n">
-        <v>7020292</v>
+        <v>7020149</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B13" t="n">
-        <v>105182</v>
+        <v>100428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R13" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B14" t="n">
-        <v>100428</v>
+        <v>105182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R14" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126089652</v>
+        <v>126092279</v>
       </c>
       <c r="B8" t="n">
-        <v>103396</v>
+        <v>100428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609923</v>
+        <v>610202</v>
       </c>
       <c r="R8" t="n">
-        <v>7020292</v>
+        <v>7020149</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126092279</v>
+        <v>126089652</v>
       </c>
       <c r="B9" t="n">
-        <v>100428</v>
+        <v>103396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610202</v>
+        <v>609923</v>
       </c>
       <c r="R9" t="n">
-        <v>7020149</v>
+        <v>7020292</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B13" t="n">
-        <v>100428</v>
+        <v>105182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R13" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B14" t="n">
-        <v>105182</v>
+        <v>100428</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R14" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091696</v>
+        <v>126090465</v>
       </c>
       <c r="B27" t="n">
-        <v>103396</v>
+        <v>100428</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>610047</v>
+        <v>609876</v>
       </c>
       <c r="R27" t="n">
-        <v>7020226</v>
+        <v>7020328</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126090465</v>
+        <v>126092414</v>
       </c>
       <c r="B28" t="n">
         <v>100428</v>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609876</v>
+        <v>610159</v>
       </c>
       <c r="R28" t="n">
-        <v>7020328</v>
+        <v>7020117</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126092414</v>
+        <v>126091696</v>
       </c>
       <c r="B29" t="n">
-        <v>100428</v>
+        <v>103396</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,16 +3305,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610159</v>
+        <v>610047</v>
       </c>
       <c r="R29" t="n">
-        <v>7020117</v>
+        <v>7020226</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091848</v>
       </c>
       <c r="B2" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126090563</v>
       </c>
       <c r="B3" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092313</v>
       </c>
       <c r="B4" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126092513</v>
       </c>
       <c r="B5" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126091604</v>
       </c>
       <c r="B6" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126091741</v>
       </c>
       <c r="B7" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126092279</v>
+        <v>126089652</v>
       </c>
       <c r="B8" t="n">
-        <v>100428</v>
+        <v>103398</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610202</v>
+        <v>609923</v>
       </c>
       <c r="R8" t="n">
-        <v>7020149</v>
+        <v>7020292</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126089652</v>
+        <v>126092279</v>
       </c>
       <c r="B9" t="n">
-        <v>103396</v>
+        <v>100430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609923</v>
+        <v>610202</v>
       </c>
       <c r="R9" t="n">
-        <v>7020292</v>
+        <v>7020149</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126090793</v>
+        <v>126091900</v>
       </c>
       <c r="B10" t="n">
-        <v>103396</v>
+        <v>100430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609929</v>
+        <v>610133</v>
       </c>
       <c r="R10" t="n">
-        <v>7020293</v>
+        <v>7020150</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091900</v>
+        <v>126090793</v>
       </c>
       <c r="B11" t="n">
-        <v>100428</v>
+        <v>103398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610133</v>
+        <v>609929</v>
       </c>
       <c r="R11" t="n">
-        <v>7020150</v>
+        <v>7020293</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1648,7 +1648,7 @@
         <v>126091974</v>
       </c>
       <c r="B12" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B13" t="n">
-        <v>105182</v>
+        <v>100430</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R13" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B14" t="n">
-        <v>100428</v>
+        <v>105184</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R14" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1939,7 +1939,7 @@
         <v>126089443</v>
       </c>
       <c r="B15" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>126090197</v>
       </c>
       <c r="B16" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091802</v>
+        <v>126091251</v>
       </c>
       <c r="B17" t="n">
-        <v>105182</v>
+        <v>100430</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610110</v>
+        <v>609946</v>
       </c>
       <c r="R17" t="n">
-        <v>7020178</v>
+        <v>7020274</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091251</v>
+        <v>126089826</v>
       </c>
       <c r="B18" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609946</v>
+        <v>609916</v>
       </c>
       <c r="R18" t="n">
-        <v>7020274</v>
+        <v>7020317</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126089826</v>
+        <v>126091802</v>
       </c>
       <c r="B19" t="n">
-        <v>100428</v>
+        <v>105184</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609916</v>
+        <v>610110</v>
       </c>
       <c r="R19" t="n">
-        <v>7020317</v>
+        <v>7020178</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2424,7 +2424,7 @@
         <v>126090758</v>
       </c>
       <c r="B20" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126091989</v>
       </c>
       <c r="B21" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126091759</v>
       </c>
       <c r="B22" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126090677</v>
       </c>
       <c r="B23" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126091224</v>
       </c>
       <c r="B24" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126090868</v>
       </c>
       <c r="B25" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126091958</v>
       </c>
       <c r="B26" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126090465</v>
       </c>
       <c r="B27" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>126092414</v>
       </c>
       <c r="B28" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>126091696</v>
       </c>
       <c r="B29" t="n">
-        <v>103396</v>
+        <v>103398</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091251</v>
+        <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>100430</v>
+        <v>105184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609946</v>
+        <v>610110</v>
       </c>
       <c r="R17" t="n">
-        <v>7020274</v>
+        <v>7020178</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126089826</v>
+        <v>126091251</v>
       </c>
       <c r="B18" t="n">
         <v>100430</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609916</v>
+        <v>609946</v>
       </c>
       <c r="R18" t="n">
-        <v>7020317</v>
+        <v>7020274</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091802</v>
+        <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>105184</v>
+        <v>100430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>610110</v>
+        <v>609916</v>
       </c>
       <c r="R19" t="n">
-        <v>7020178</v>
+        <v>7020317</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091848</v>
+        <v>126090563</v>
       </c>
       <c r="B2" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610126</v>
+        <v>609902</v>
       </c>
       <c r="R2" t="n">
-        <v>7020167</v>
+        <v>7020332</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126090563</v>
+        <v>126092313</v>
       </c>
       <c r="B3" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609902</v>
+        <v>610186</v>
       </c>
       <c r="R3" t="n">
-        <v>7020332</v>
+        <v>7020158</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126092313</v>
+        <v>126091848</v>
       </c>
       <c r="B4" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610186</v>
+        <v>610126</v>
       </c>
       <c r="R4" t="n">
-        <v>7020158</v>
+        <v>7020167</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>126092513</v>
       </c>
       <c r="B5" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126091604</v>
       </c>
       <c r="B6" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126091741</v>
       </c>
       <c r="B7" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126089652</v>
       </c>
       <c r="B8" t="n">
-        <v>103398</v>
+        <v>103400</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126092279</v>
       </c>
       <c r="B9" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>126091900</v>
       </c>
       <c r="B10" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126090793</v>
+        <v>126091974</v>
       </c>
       <c r="B11" t="n">
-        <v>103398</v>
+        <v>100432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609929</v>
+        <v>610174</v>
       </c>
       <c r="R11" t="n">
-        <v>7020293</v>
+        <v>7020149</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091974</v>
+        <v>126090793</v>
       </c>
       <c r="B12" t="n">
-        <v>100430</v>
+        <v>103400</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610174</v>
+        <v>609929</v>
       </c>
       <c r="R12" t="n">
-        <v>7020149</v>
+        <v>7020293</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B13" t="n">
-        <v>100430</v>
+        <v>105186</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R13" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B14" t="n">
-        <v>105184</v>
+        <v>100432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R14" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1939,7 +1939,7 @@
         <v>126089443</v>
       </c>
       <c r="B15" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>126090197</v>
       </c>
       <c r="B16" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>105184</v>
+        <v>105186</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>126091251</v>
       </c>
       <c r="B18" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126090758</v>
       </c>
       <c r="B20" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126091989</v>
       </c>
       <c r="B21" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126091759</v>
       </c>
       <c r="B22" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126090677</v>
+        <v>126091224</v>
       </c>
       <c r="B23" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609919</v>
+        <v>609958</v>
       </c>
       <c r="R23" t="n">
-        <v>7020325</v>
+        <v>7020289</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091224</v>
+        <v>126090868</v>
       </c>
       <c r="B24" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609958</v>
+        <v>609934</v>
       </c>
       <c r="R24" t="n">
-        <v>7020289</v>
+        <v>7020301</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126090868</v>
+        <v>126090677</v>
       </c>
       <c r="B25" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609934</v>
+        <v>609919</v>
       </c>
       <c r="R25" t="n">
-        <v>7020301</v>
+        <v>7020325</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3006,7 +3006,7 @@
         <v>126091958</v>
       </c>
       <c r="B26" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126090465</v>
+        <v>126091696</v>
       </c>
       <c r="B27" t="n">
-        <v>100430</v>
+        <v>103400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609876</v>
+        <v>610047</v>
       </c>
       <c r="R27" t="n">
-        <v>7020328</v>
+        <v>7020226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3200,7 +3200,7 @@
         <v>126092414</v>
       </c>
       <c r="B28" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091696</v>
+        <v>126090465</v>
       </c>
       <c r="B29" t="n">
-        <v>103398</v>
+        <v>100432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,16 +3305,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610047</v>
+        <v>609876</v>
       </c>
       <c r="R29" t="n">
-        <v>7020226</v>
+        <v>7020328</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091900</v>
+        <v>126090793</v>
       </c>
       <c r="B10" t="n">
-        <v>100432</v>
+        <v>103400</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610133</v>
+        <v>609929</v>
       </c>
       <c r="R10" t="n">
-        <v>7020150</v>
+        <v>7020293</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091974</v>
+        <v>126091900</v>
       </c>
       <c r="B11" t="n">
         <v>100432</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610174</v>
+        <v>610133</v>
       </c>
       <c r="R11" t="n">
-        <v>7020149</v>
+        <v>7020150</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126090793</v>
+        <v>126091974</v>
       </c>
       <c r="B12" t="n">
-        <v>103400</v>
+        <v>100432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609929</v>
+        <v>610174</v>
       </c>
       <c r="R12" t="n">
-        <v>7020293</v>
+        <v>7020149</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091802</v>
+        <v>126091251</v>
       </c>
       <c r="B17" t="n">
-        <v>105186</v>
+        <v>100432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610110</v>
+        <v>609946</v>
       </c>
       <c r="R17" t="n">
-        <v>7020178</v>
+        <v>7020274</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091251</v>
+        <v>126089826</v>
       </c>
       <c r="B18" t="n">
         <v>100432</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609946</v>
+        <v>609916</v>
       </c>
       <c r="R18" t="n">
-        <v>7020274</v>
+        <v>7020317</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126089826</v>
+        <v>126091802</v>
       </c>
       <c r="B19" t="n">
-        <v>100432</v>
+        <v>105186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609916</v>
+        <v>610110</v>
       </c>
       <c r="R19" t="n">
-        <v>7020317</v>
+        <v>7020178</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126090563</v>
+        <v>126091848</v>
       </c>
       <c r="B2" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609902</v>
+        <v>610126</v>
       </c>
       <c r="R2" t="n">
-        <v>7020332</v>
+        <v>7020167</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126092313</v>
+        <v>126090563</v>
       </c>
       <c r="B3" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610186</v>
+        <v>609902</v>
       </c>
       <c r="R3" t="n">
-        <v>7020158</v>
+        <v>7020332</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091848</v>
+        <v>126092313</v>
       </c>
       <c r="B4" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610126</v>
+        <v>610186</v>
       </c>
       <c r="R4" t="n">
-        <v>7020167</v>
+        <v>7020158</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -969,7 +969,7 @@
         <v>126092513</v>
       </c>
       <c r="B5" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126091604</v>
       </c>
       <c r="B6" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126091741</v>
       </c>
       <c r="B7" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126089652</v>
+        <v>126092279</v>
       </c>
       <c r="B8" t="n">
-        <v>103400</v>
+        <v>100434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609923</v>
+        <v>610202</v>
       </c>
       <c r="R8" t="n">
-        <v>7020292</v>
+        <v>7020149</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126092279</v>
+        <v>126089652</v>
       </c>
       <c r="B9" t="n">
-        <v>100432</v>
+        <v>103404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610202</v>
+        <v>609923</v>
       </c>
       <c r="R9" t="n">
-        <v>7020149</v>
+        <v>7020292</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1454,7 +1454,7 @@
         <v>126090793</v>
       </c>
       <c r="B10" t="n">
-        <v>103400</v>
+        <v>103404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>126091900</v>
       </c>
       <c r="B11" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>126091974</v>
       </c>
       <c r="B12" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126091481</v>
       </c>
       <c r="B13" t="n">
-        <v>105186</v>
+        <v>105190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126092468</v>
       </c>
       <c r="B14" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>126089443</v>
       </c>
       <c r="B15" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>126090197</v>
       </c>
       <c r="B16" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091251</v>
+        <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>100432</v>
+        <v>105190</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609946</v>
+        <v>610110</v>
       </c>
       <c r="R17" t="n">
-        <v>7020274</v>
+        <v>7020178</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126089826</v>
+        <v>126091251</v>
       </c>
       <c r="B18" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609916</v>
+        <v>609946</v>
       </c>
       <c r="R18" t="n">
-        <v>7020317</v>
+        <v>7020274</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091802</v>
+        <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>105186</v>
+        <v>100434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>610110</v>
+        <v>609916</v>
       </c>
       <c r="R19" t="n">
-        <v>7020178</v>
+        <v>7020317</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2424,7 +2424,7 @@
         <v>126090758</v>
       </c>
       <c r="B20" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126091989</v>
       </c>
       <c r="B21" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126091759</v>
       </c>
       <c r="B22" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2712,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126091224</v>
+        <v>126090677</v>
       </c>
       <c r="B23" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609958</v>
+        <v>609919</v>
       </c>
       <c r="R23" t="n">
-        <v>7020289</v>
+        <v>7020325</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126090868</v>
+        <v>126091224</v>
       </c>
       <c r="B24" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609934</v>
+        <v>609958</v>
       </c>
       <c r="R24" t="n">
-        <v>7020301</v>
+        <v>7020289</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126090677</v>
+        <v>126090868</v>
       </c>
       <c r="B25" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609919</v>
+        <v>609934</v>
       </c>
       <c r="R25" t="n">
-        <v>7020325</v>
+        <v>7020301</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3006,7 +3006,7 @@
         <v>126091958</v>
       </c>
       <c r="B26" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126091696</v>
       </c>
       <c r="B27" t="n">
-        <v>103400</v>
+        <v>103404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126092414</v>
+        <v>126090465</v>
       </c>
       <c r="B28" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>610159</v>
+        <v>609876</v>
       </c>
       <c r="R28" t="n">
-        <v>7020117</v>
+        <v>7020328</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126090465</v>
+        <v>126092414</v>
       </c>
       <c r="B29" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609876</v>
+        <v>610159</v>
       </c>
       <c r="R29" t="n">
-        <v>7020328</v>
+        <v>7020117</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B13" t="n">
-        <v>105190</v>
+        <v>100434</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R13" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B14" t="n">
-        <v>100434</v>
+        <v>105190</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R14" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091848</v>
       </c>
       <c r="B2" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126090563</v>
       </c>
       <c r="B3" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092313</v>
       </c>
       <c r="B4" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126092513</v>
       </c>
       <c r="B5" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126091604</v>
       </c>
       <c r="B6" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126091741</v>
       </c>
       <c r="B7" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126092279</v>
       </c>
       <c r="B8" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126089652</v>
       </c>
       <c r="B9" t="n">
-        <v>103404</v>
+        <v>103417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126090793</v>
+        <v>126091900</v>
       </c>
       <c r="B10" t="n">
-        <v>103404</v>
+        <v>100438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609929</v>
+        <v>610133</v>
       </c>
       <c r="R10" t="n">
-        <v>7020293</v>
+        <v>7020150</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091900</v>
+        <v>126091974</v>
       </c>
       <c r="B11" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610133</v>
+        <v>610174</v>
       </c>
       <c r="R11" t="n">
-        <v>7020150</v>
+        <v>7020149</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091974</v>
+        <v>126090793</v>
       </c>
       <c r="B12" t="n">
-        <v>100434</v>
+        <v>103417</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610174</v>
+        <v>609929</v>
       </c>
       <c r="R12" t="n">
-        <v>7020149</v>
+        <v>7020293</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B13" t="n">
-        <v>100434</v>
+        <v>105203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R13" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B14" t="n">
-        <v>105190</v>
+        <v>100438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R14" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1939,7 +1939,7 @@
         <v>126089443</v>
       </c>
       <c r="B15" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>126090197</v>
       </c>
       <c r="B16" t="n">
-        <v>97223</v>
+        <v>97227</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>105190</v>
+        <v>105203</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>126091251</v>
       </c>
       <c r="B18" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126090758</v>
       </c>
       <c r="B20" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126091989</v>
       </c>
       <c r="B21" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126091759</v>
       </c>
       <c r="B22" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126090677</v>
       </c>
       <c r="B23" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126091224</v>
       </c>
       <c r="B24" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126090868</v>
       </c>
       <c r="B25" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126091958</v>
       </c>
       <c r="B26" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091696</v>
+        <v>126090465</v>
       </c>
       <c r="B27" t="n">
-        <v>103404</v>
+        <v>100438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>610047</v>
+        <v>609876</v>
       </c>
       <c r="R27" t="n">
-        <v>7020226</v>
+        <v>7020328</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126090465</v>
+        <v>126091696</v>
       </c>
       <c r="B28" t="n">
-        <v>100434</v>
+        <v>103417</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,16 +3208,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609876</v>
+        <v>610047</v>
       </c>
       <c r="R28" t="n">
-        <v>7020328</v>
+        <v>7020226</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>126092414</v>
       </c>
       <c r="B29" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091848</v>
       </c>
       <c r="B2" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126090563</v>
       </c>
       <c r="B3" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092313</v>
       </c>
       <c r="B4" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126092513</v>
       </c>
       <c r="B5" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126091604</v>
       </c>
       <c r="B6" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126091741</v>
       </c>
       <c r="B7" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126092279</v>
+        <v>126089652</v>
       </c>
       <c r="B8" t="n">
-        <v>100438</v>
+        <v>103420</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,16 +1268,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>610202</v>
+        <v>609923</v>
       </c>
       <c r="R8" t="n">
-        <v>7020149</v>
+        <v>7020292</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126089652</v>
+        <v>126092279</v>
       </c>
       <c r="B9" t="n">
-        <v>103417</v>
+        <v>100441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>609923</v>
+        <v>610202</v>
       </c>
       <c r="R9" t="n">
-        <v>7020292</v>
+        <v>7020149</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1454,7 +1454,7 @@
         <v>126091900</v>
       </c>
       <c r="B10" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091974</v>
+        <v>126090793</v>
       </c>
       <c r="B11" t="n">
-        <v>100438</v>
+        <v>103420</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610174</v>
+        <v>609929</v>
       </c>
       <c r="R11" t="n">
-        <v>7020149</v>
+        <v>7020293</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126090793</v>
+        <v>126091974</v>
       </c>
       <c r="B12" t="n">
-        <v>103417</v>
+        <v>100441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,16 +1656,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>609929</v>
+        <v>610174</v>
       </c>
       <c r="R12" t="n">
-        <v>7020293</v>
+        <v>7020149</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B13" t="n">
-        <v>105203</v>
+        <v>100441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R13" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B14" t="n">
-        <v>100438</v>
+        <v>105206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R14" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1939,7 +1939,7 @@
         <v>126089443</v>
       </c>
       <c r="B15" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>126090197</v>
       </c>
       <c r="B16" t="n">
-        <v>97227</v>
+        <v>97230</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091802</v>
+        <v>126091251</v>
       </c>
       <c r="B17" t="n">
-        <v>105203</v>
+        <v>100441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610110</v>
+        <v>609946</v>
       </c>
       <c r="R17" t="n">
-        <v>7020178</v>
+        <v>7020274</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091251</v>
+        <v>126089826</v>
       </c>
       <c r="B18" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609946</v>
+        <v>609916</v>
       </c>
       <c r="R18" t="n">
-        <v>7020274</v>
+        <v>7020317</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126089826</v>
+        <v>126091802</v>
       </c>
       <c r="B19" t="n">
-        <v>100438</v>
+        <v>105206</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609916</v>
+        <v>610110</v>
       </c>
       <c r="R19" t="n">
-        <v>7020317</v>
+        <v>7020178</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2424,7 +2424,7 @@
         <v>126090758</v>
       </c>
       <c r="B20" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126091989</v>
       </c>
       <c r="B21" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126091759</v>
       </c>
       <c r="B22" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126090677</v>
       </c>
       <c r="B23" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126091224</v>
       </c>
       <c r="B24" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126090868</v>
       </c>
       <c r="B25" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126091958</v>
       </c>
       <c r="B26" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
         <v>126090465</v>
       </c>
       <c r="B27" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126091696</v>
+        <v>126092414</v>
       </c>
       <c r="B28" t="n">
-        <v>103417</v>
+        <v>100441</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3208,16 +3208,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>610047</v>
+        <v>610159</v>
       </c>
       <c r="R28" t="n">
-        <v>7020226</v>
+        <v>7020117</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126092414</v>
+        <v>126091696</v>
       </c>
       <c r="B29" t="n">
-        <v>100438</v>
+        <v>103420</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,16 +3305,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610159</v>
+        <v>610047</v>
       </c>
       <c r="R29" t="n">
-        <v>7020117</v>
+        <v>7020226</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091900</v>
+        <v>126090793</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>103420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610133</v>
+        <v>609929</v>
       </c>
       <c r="R10" t="n">
-        <v>7020150</v>
+        <v>7020293</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126090793</v>
+        <v>126091900</v>
       </c>
       <c r="B11" t="n">
-        <v>103420</v>
+        <v>100441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609929</v>
+        <v>610133</v>
       </c>
       <c r="R11" t="n">
-        <v>7020293</v>
+        <v>7020150</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126092468</v>
+        <v>126091481</v>
       </c>
       <c r="B13" t="n">
-        <v>100441</v>
+        <v>105206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>610149</v>
+        <v>609967</v>
       </c>
       <c r="R13" t="n">
-        <v>7020112</v>
+        <v>7020285</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126091481</v>
+        <v>126092468</v>
       </c>
       <c r="B14" t="n">
-        <v>105206</v>
+        <v>100441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,16 +1850,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>609967</v>
+        <v>610149</v>
       </c>
       <c r="R14" t="n">
-        <v>7020285</v>
+        <v>7020112</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126090465</v>
+        <v>126091696</v>
       </c>
       <c r="B27" t="n">
-        <v>100441</v>
+        <v>103420</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609876</v>
+        <v>610047</v>
       </c>
       <c r="R27" t="n">
-        <v>7020328</v>
+        <v>7020226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126092414</v>
+        <v>126090465</v>
       </c>
       <c r="B28" t="n">
         <v>100441</v>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>610159</v>
+        <v>609876</v>
       </c>
       <c r="R28" t="n">
-        <v>7020117</v>
+        <v>7020328</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091696</v>
+        <v>126092414</v>
       </c>
       <c r="B29" t="n">
-        <v>103420</v>
+        <v>100441</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,16 +3305,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610047</v>
+        <v>610159</v>
       </c>
       <c r="R29" t="n">
-        <v>7020226</v>
+        <v>7020117</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091251</v>
+        <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>100441</v>
+        <v>105206</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609946</v>
+        <v>610110</v>
       </c>
       <c r="R17" t="n">
-        <v>7020274</v>
+        <v>7020178</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126089826</v>
+        <v>126091251</v>
       </c>
       <c r="B18" t="n">
         <v>100441</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609916</v>
+        <v>609946</v>
       </c>
       <c r="R18" t="n">
-        <v>7020317</v>
+        <v>7020274</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091802</v>
+        <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>105206</v>
+        <v>100441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>610110</v>
+        <v>609916</v>
       </c>
       <c r="R19" t="n">
-        <v>7020178</v>
+        <v>7020317</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126091848</v>
       </c>
       <c r="B2" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126090563</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126092313</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126092513</v>
       </c>
       <c r="B5" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>126091604</v>
       </c>
       <c r="B6" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>126091741</v>
       </c>
       <c r="B7" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>126089652</v>
       </c>
       <c r="B8" t="n">
-        <v>103420</v>
+        <v>103429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>126092279</v>
       </c>
       <c r="B9" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126090793</v>
+        <v>126091900</v>
       </c>
       <c r="B10" t="n">
-        <v>103420</v>
+        <v>100450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609929</v>
+        <v>610133</v>
       </c>
       <c r="R10" t="n">
-        <v>7020293</v>
+        <v>7020150</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091900</v>
+        <v>126090793</v>
       </c>
       <c r="B11" t="n">
-        <v>100441</v>
+        <v>103429</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610133</v>
+        <v>609929</v>
       </c>
       <c r="R11" t="n">
-        <v>7020150</v>
+        <v>7020293</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1648,7 +1648,7 @@
         <v>126091974</v>
       </c>
       <c r="B12" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>126091481</v>
       </c>
       <c r="B13" t="n">
-        <v>105206</v>
+        <v>105215</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>126092468</v>
       </c>
       <c r="B14" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>126089443</v>
       </c>
       <c r="B15" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>126090197</v>
       </c>
       <c r="B16" t="n">
-        <v>97230</v>
+        <v>97239</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>105206</v>
+        <v>105215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>126091251</v>
       </c>
       <c r="B18" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>126090758</v>
       </c>
       <c r="B20" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2521,7 +2521,7 @@
         <v>126091989</v>
       </c>
       <c r="B21" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>126091759</v>
       </c>
       <c r="B22" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>126090677</v>
       </c>
       <c r="B23" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2812,7 +2812,7 @@
         <v>126091224</v>
       </c>
       <c r="B24" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2909,7 +2909,7 @@
         <v>126090868</v>
       </c>
       <c r="B25" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>126091958</v>
       </c>
       <c r="B26" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091696</v>
+        <v>126090465</v>
       </c>
       <c r="B27" t="n">
-        <v>103420</v>
+        <v>100450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>610047</v>
+        <v>609876</v>
       </c>
       <c r="R27" t="n">
-        <v>7020226</v>
+        <v>7020328</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126090465</v>
+        <v>126092414</v>
       </c>
       <c r="B28" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,13 +3232,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>609876</v>
+        <v>610159</v>
       </c>
       <c r="R28" t="n">
-        <v>7020328</v>
+        <v>7020117</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126092414</v>
+        <v>126091696</v>
       </c>
       <c r="B29" t="n">
-        <v>100441</v>
+        <v>103429</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,16 +3305,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3329,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610159</v>
+        <v>610047</v>
       </c>
       <c r="R29" t="n">
-        <v>7020117</v>
+        <v>7020226</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126091848</v>
+        <v>126090563</v>
       </c>
       <c r="B2" t="n">
         <v>100450</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>610126</v>
+        <v>609902</v>
       </c>
       <c r="R2" t="n">
-        <v>7020167</v>
+        <v>7020332</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126090563</v>
+        <v>126092313</v>
       </c>
       <c r="B3" t="n">
         <v>100450</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>609902</v>
+        <v>610186</v>
       </c>
       <c r="R3" t="n">
-        <v>7020332</v>
+        <v>7020158</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126092313</v>
+        <v>126091848</v>
       </c>
       <c r="B4" t="n">
         <v>100450</v>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610186</v>
+        <v>610126</v>
       </c>
       <c r="R4" t="n">
-        <v>7020158</v>
+        <v>7020167</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126091900</v>
+        <v>126090793</v>
       </c>
       <c r="B10" t="n">
-        <v>100450</v>
+        <v>103429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,16 +1462,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>610133</v>
+        <v>609929</v>
       </c>
       <c r="R10" t="n">
-        <v>7020150</v>
+        <v>7020293</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126090793</v>
+        <v>126091900</v>
       </c>
       <c r="B11" t="n">
-        <v>103429</v>
+        <v>100450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>609929</v>
+        <v>610133</v>
       </c>
       <c r="R11" t="n">
-        <v>7020293</v>
+        <v>7020150</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091802</v>
+        <v>126091251</v>
       </c>
       <c r="B17" t="n">
-        <v>105215</v>
+        <v>100450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610110</v>
+        <v>609946</v>
       </c>
       <c r="R17" t="n">
-        <v>7020178</v>
+        <v>7020274</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091251</v>
+        <v>126089826</v>
       </c>
       <c r="B18" t="n">
         <v>100450</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609946</v>
+        <v>609916</v>
       </c>
       <c r="R18" t="n">
-        <v>7020274</v>
+        <v>7020317</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126089826</v>
+        <v>126091802</v>
       </c>
       <c r="B19" t="n">
-        <v>100450</v>
+        <v>105215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609916</v>
+        <v>610110</v>
       </c>
       <c r="R19" t="n">
-        <v>7020317</v>
+        <v>7020178</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126090677</v>
+        <v>126091224</v>
       </c>
       <c r="B23" t="n">
         <v>100450</v>
@@ -2747,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>609919</v>
+        <v>609958</v>
       </c>
       <c r="R23" t="n">
-        <v>7020325</v>
+        <v>7020289</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126091224</v>
+        <v>126090868</v>
       </c>
       <c r="B24" t="n">
         <v>100450</v>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609958</v>
+        <v>609934</v>
       </c>
       <c r="R24" t="n">
-        <v>7020289</v>
+        <v>7020301</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2906,7 +2906,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126090868</v>
+        <v>126090677</v>
       </c>
       <c r="B25" t="n">
         <v>100450</v>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609934</v>
+        <v>609919</v>
       </c>
       <c r="R25" t="n">
-        <v>7020301</v>
+        <v>7020325</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126090465</v>
+        <v>126091696</v>
       </c>
       <c r="B27" t="n">
-        <v>100450</v>
+        <v>103429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,13 +3135,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>609876</v>
+        <v>610047</v>
       </c>
       <c r="R27" t="n">
-        <v>7020328</v>
+        <v>7020226</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126091696</v>
+        <v>126090465</v>
       </c>
       <c r="B29" t="n">
-        <v>103429</v>
+        <v>100450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3305,16 +3305,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>610047</v>
+        <v>609876</v>
       </c>
       <c r="R29" t="n">
-        <v>7020226</v>
+        <v>7020328</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091251</v>
+        <v>126091802</v>
       </c>
       <c r="B17" t="n">
-        <v>100450</v>
+        <v>105215</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>609946</v>
+        <v>610110</v>
       </c>
       <c r="R17" t="n">
-        <v>7020274</v>
+        <v>7020178</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126089826</v>
+        <v>126091251</v>
       </c>
       <c r="B18" t="n">
         <v>100450</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609916</v>
+        <v>609946</v>
       </c>
       <c r="R18" t="n">
-        <v>7020317</v>
+        <v>7020274</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126091802</v>
+        <v>126089826</v>
       </c>
       <c r="B19" t="n">
-        <v>105215</v>
+        <v>100450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>610110</v>
+        <v>609916</v>
       </c>
       <c r="R19" t="n">
-        <v>7020178</v>
+        <v>7020317</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091802</v>
+        <v>126091251</v>
       </c>
       <c r="B17" t="n">
-        <v>105215</v>
+        <v>100450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610110</v>
+        <v>609946</v>
       </c>
       <c r="R17" t="n">
-        <v>7020178</v>
+        <v>7020274</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091251</v>
+        <v>126089826</v>
       </c>
       <c r="B18" t="n">
         <v>100450</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609946</v>
+        <v>609916</v>
       </c>
       <c r="R18" t="n">
-        <v>7020274</v>
+        <v>7020317</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126089826</v>
+        <v>126091802</v>
       </c>
       <c r="B19" t="n">
-        <v>100450</v>
+        <v>105215</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2335,16 +2335,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609916</v>
+        <v>610110</v>
       </c>
       <c r="R19" t="n">
-        <v>7020317</v>
+        <v>7020178</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126090563</v>
+        <v>126089021</v>
       </c>
       <c r="B2" t="n">
-        <v>100450</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>609902</v>
+        <v>609865</v>
       </c>
       <c r="R2" t="n">
-        <v>7020332</v>
+        <v>7020261</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126092313</v>
+        <v>126091135</v>
       </c>
       <c r="B3" t="n">
-        <v>100450</v>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>610186</v>
+        <v>609961</v>
       </c>
       <c r="R3" t="n">
-        <v>7020158</v>
+        <v>7020297</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126091848</v>
+        <v>126091481</v>
       </c>
       <c r="B4" t="n">
-        <v>100450</v>
+        <v>106061</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,16 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610126</v>
+        <v>609967</v>
       </c>
       <c r="R4" t="n">
-        <v>7020167</v>
+        <v>7020285</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126092513</v>
+        <v>126091802</v>
       </c>
       <c r="B5" t="n">
-        <v>100450</v>
+        <v>106061</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>221101</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Springkorn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Impatiens noli-tangere</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>610128</v>
+        <v>610110</v>
       </c>
       <c r="R5" t="n">
-        <v>7020092</v>
+        <v>7020178</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126091604</v>
+        <v>126090197</v>
       </c>
       <c r="B6" t="n">
-        <v>100450</v>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,16 +1074,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222771</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>610001</v>
+        <v>609878</v>
       </c>
       <c r="R6" t="n">
-        <v>7020250</v>
+        <v>7020293</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126091741</v>
+        <v>126089652</v>
       </c>
       <c r="B7" t="n">
-        <v>100450</v>
+        <v>104253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>610079</v>
+        <v>609923</v>
       </c>
       <c r="R7" t="n">
-        <v>7020222</v>
+        <v>7020292</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126089652</v>
+        <v>126090608</v>
       </c>
       <c r="B8" t="n">
-        <v>103429</v>
+        <v>104253</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>609923</v>
+        <v>609903</v>
       </c>
       <c r="R8" t="n">
-        <v>7020292</v>
+        <v>7020340</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126092279</v>
+        <v>126090793</v>
       </c>
       <c r="B9" t="n">
-        <v>100450</v>
+        <v>104253</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,16 +1365,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>222395</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Dvärghäxört</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Circaea alpina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>610202</v>
+        <v>609929</v>
       </c>
       <c r="R9" t="n">
-        <v>7020149</v>
+        <v>7020293</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126090793</v>
+        <v>126091696</v>
       </c>
       <c r="B10" t="n">
-        <v>103429</v>
+        <v>104253</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>609929</v>
+        <v>610047</v>
       </c>
       <c r="R10" t="n">
-        <v>7020293</v>
+        <v>7020226</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126091900</v>
+        <v>126089284</v>
       </c>
       <c r="B11" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>610133</v>
+        <v>609882</v>
       </c>
       <c r="R11" t="n">
-        <v>7020150</v>
+        <v>7020253</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1645,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126091974</v>
+        <v>126089328</v>
       </c>
       <c r="B12" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>610174</v>
+        <v>609877</v>
       </c>
       <c r="R12" t="n">
-        <v>7020149</v>
+        <v>7020268</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126091481</v>
+        <v>126089360</v>
       </c>
       <c r="B13" t="n">
-        <v>105215</v>
+        <v>101228</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1753,16 +1753,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1777,13 +1777,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>609967</v>
+        <v>609899</v>
       </c>
       <c r="R13" t="n">
-        <v>7020285</v>
+        <v>7020262</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126092468</v>
+        <v>126089443</v>
       </c>
       <c r="B14" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>610149</v>
+        <v>609913</v>
       </c>
       <c r="R14" t="n">
-        <v>7020112</v>
+        <v>7020279</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126089443</v>
+        <v>126089826</v>
       </c>
       <c r="B15" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>609913</v>
+        <v>609916</v>
       </c>
       <c r="R15" t="n">
-        <v>7020279</v>
+        <v>7020317</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126090197</v>
+        <v>126090465</v>
       </c>
       <c r="B16" t="n">
-        <v>97239</v>
+        <v>101228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,16 +2044,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2068,13 +2068,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>609878</v>
+        <v>609876</v>
       </c>
       <c r="R16" t="n">
-        <v>7020293</v>
+        <v>7020328</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126091802</v>
+        <v>126090563</v>
       </c>
       <c r="B17" t="n">
-        <v>105215</v>
+        <v>101228</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,16 +2141,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221101</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springkorn</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Impatiens noli-tangere</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>610110</v>
+        <v>609902</v>
       </c>
       <c r="R17" t="n">
-        <v>7020178</v>
+        <v>7020332</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2227,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126091251</v>
+        <v>126090677</v>
       </c>
       <c r="B18" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>609946</v>
+        <v>609919</v>
       </c>
       <c r="R18" t="n">
-        <v>7020274</v>
+        <v>7020325</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126089826</v>
+        <v>126090758</v>
       </c>
       <c r="B19" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>609916</v>
+        <v>609938</v>
       </c>
       <c r="R19" t="n">
-        <v>7020317</v>
+        <v>7020289</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126090758</v>
+        <v>126090868</v>
       </c>
       <c r="B20" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>609938</v>
+        <v>609934</v>
       </c>
       <c r="R20" t="n">
-        <v>7020289</v>
+        <v>7020301</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2518,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126091989</v>
+        <v>126090912</v>
       </c>
       <c r="B21" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>610165</v>
+        <v>609938</v>
       </c>
       <c r="R21" t="n">
-        <v>7020164</v>
+        <v>7020316</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2615,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126091759</v>
+        <v>126090934</v>
       </c>
       <c r="B22" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>610090</v>
+        <v>609959</v>
       </c>
       <c r="R22" t="n">
-        <v>7020200</v>
+        <v>7020299</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2715,7 +2715,7 @@
         <v>126091224</v>
       </c>
       <c r="B23" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2809,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126090868</v>
+        <v>126091251</v>
       </c>
       <c r="B24" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>609934</v>
+        <v>609946</v>
       </c>
       <c r="R24" t="n">
-        <v>7020301</v>
+        <v>7020274</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2906,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126090677</v>
+        <v>126091554</v>
       </c>
       <c r="B25" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>609919</v>
+        <v>609954</v>
       </c>
       <c r="R25" t="n">
-        <v>7020325</v>
+        <v>7020248</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3003,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126091958</v>
+        <v>126091604</v>
       </c>
       <c r="B26" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3038,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>610148</v>
+        <v>610001</v>
       </c>
       <c r="R26" t="n">
-        <v>7020132</v>
+        <v>7020250</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>126091696</v>
+        <v>126091718</v>
       </c>
       <c r="B27" t="n">
-        <v>103429</v>
+        <v>101228</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3111,16 +3111,16 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222395</v>
+        <v>222771</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärghäxört</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Circaea alpina</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>610047</v>
+        <v>610061</v>
       </c>
       <c r="R27" t="n">
-        <v>7020226</v>
+        <v>7020224</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>126092414</v>
+        <v>126091741</v>
       </c>
       <c r="B28" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3232,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>610159</v>
+        <v>610079</v>
       </c>
       <c r="R28" t="n">
-        <v>7020117</v>
+        <v>7020222</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3294,10 +3294,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126090465</v>
+        <v>126091759</v>
       </c>
       <c r="B29" t="n">
-        <v>100450</v>
+        <v>101228</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3329,13 +3329,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>609876</v>
+        <v>610090</v>
       </c>
       <c r="R29" t="n">
-        <v>7020328</v>
+        <v>7020200</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3388,6 +3388,976 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126091848</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>610126</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7020167</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126091900</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>610133</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7020150</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126091958</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>610148</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7020132</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126091974</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>610174</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7020149</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126091989</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>610165</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7020164</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126092279</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>610202</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7020149</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126092313</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>610186</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7020158</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126092414</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>610159</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7020117</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126092468</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>610149</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7020112</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126092513</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Svedjom, Svedjom, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>610128</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7020092</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-20</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25954-2025 artfynd.xlsx
+++ b/artfynd/A 25954-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089021</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091135</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091481</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091802</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090197</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090608</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090793</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091696</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089284</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089328</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089360</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089443</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126089826</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090465</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090563</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090677</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090758</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090868</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090912</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126090934</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091224</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091251</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091554</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091604</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091718</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091741</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091759</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091848</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091900</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091958</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091974</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126091989</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092279</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092313</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092414</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092468</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,8 +4548,53 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126092513</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>